--- a/docs/StructureDefinition-space-molecular-sequence.xlsx
+++ b/docs/StructureDefinition-space-molecular-sequence.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-molecular-sequence.xlsx
+++ b/docs/StructureDefinition-space-molecular-sequence.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3441" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3442" uniqueCount="417">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/space-molecular-sequence</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/space-molecular-sequence</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -506,7 +509,7 @@
     <t>MolecularSequence.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -1555,54 +1558,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1630,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="60.8515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.62109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1656,126 +1661,126 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1783,10 +1788,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1798,13 +1803,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1855,33 +1860,33 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1889,10 +1894,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1901,19 +1906,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1963,13 +1968,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1986,10 +1991,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1997,10 +2002,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2009,16 +2014,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2069,19 +2074,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2092,10 +2097,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2103,31 +2108,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2177,19 +2182,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2200,10 +2205,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2211,10 +2216,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2226,16 +2231,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2261,13 +2266,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2285,19 +2290,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2308,21 +2313,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2334,16 +2339,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2393,44 +2398,44 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2442,16 +2447,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2501,13 +2506,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2519,26 +2524,26 @@
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2550,16 +2555,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2609,68 +2614,68 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -2719,33 +2724,33 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2753,10 +2758,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2765,20 +2770,20 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2827,22 +2832,22 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
@@ -2850,10 +2855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2861,28 +2866,28 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2909,13 +2914,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -2933,19 +2938,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2956,10 +2961,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2967,10 +2972,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2979,16 +2984,16 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3039,19 +3044,19 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -3062,10 +3067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3073,28 +3078,28 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3145,19 +3150,19 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
@@ -3168,10 +3173,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3179,10 +3184,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3191,16 +3196,16 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3251,19 +3256,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -3274,10 +3279,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3285,10 +3290,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3297,16 +3302,16 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3357,19 +3362,19 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -3380,10 +3385,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3391,10 +3396,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3403,16 +3408,16 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3463,19 +3468,19 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -3486,10 +3491,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3497,10 +3502,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3509,16 +3514,16 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3569,19 +3574,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3592,10 +3597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3603,28 +3608,28 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3675,19 +3680,19 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -3698,10 +3703,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3709,10 +3714,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3724,13 +3729,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3781,13 +3786,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -3799,26 +3804,26 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3830,16 +3835,16 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3889,68 +3894,68 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3999,33 +4004,33 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4033,10 +4038,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4045,16 +4050,16 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4081,13 +4086,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4105,19 +4110,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4128,10 +4133,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4139,10 +4144,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4151,16 +4156,16 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4211,19 +4216,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4234,10 +4239,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4245,10 +4250,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4257,16 +4262,16 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4293,13 +4298,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4317,19 +4322,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -4340,10 +4345,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4351,10 +4356,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4363,16 +4368,16 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4399,13 +4404,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4423,19 +4428,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -4446,10 +4451,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4457,10 +4462,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4469,16 +4474,16 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4529,19 +4534,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -4552,10 +4557,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4563,10 +4568,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4575,16 +4580,16 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4635,19 +4640,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -4658,10 +4663,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4669,10 +4674,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4681,16 +4686,16 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4717,13 +4722,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -4741,19 +4746,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -4764,10 +4769,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4775,10 +4780,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4787,16 +4792,16 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4847,19 +4852,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -4870,10 +4875,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4881,10 +4886,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -4893,16 +4898,16 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4953,19 +4958,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -4976,10 +4981,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4987,10 +4992,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -4999,16 +5004,16 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5059,19 +5064,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5082,10 +5087,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5093,10 +5098,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5108,13 +5113,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5165,13 +5170,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5183,26 +5188,26 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5214,16 +5219,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5273,68 +5278,68 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5383,33 +5388,33 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5417,10 +5422,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5429,16 +5434,16 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5489,19 +5494,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -5512,10 +5517,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5523,10 +5528,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5535,16 +5540,16 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5595,19 +5600,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -5618,10 +5623,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5629,10 +5634,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5641,16 +5646,16 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5701,19 +5706,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -5724,10 +5729,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5735,10 +5740,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -5747,16 +5752,16 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5807,19 +5812,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -5830,10 +5835,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5841,10 +5846,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -5853,16 +5858,16 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5913,19 +5918,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -5936,10 +5941,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5947,10 +5952,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -5959,16 +5964,16 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6019,19 +6024,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6042,10 +6047,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6053,10 +6058,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6065,16 +6070,16 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6125,19 +6130,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -6148,10 +6153,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6159,10 +6164,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6171,16 +6176,16 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6231,19 +6236,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -6254,10 +6259,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6265,10 +6270,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6280,13 +6285,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6337,13 +6342,13 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -6355,26 +6360,26 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6386,16 +6391,16 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6445,68 +6450,68 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -6555,33 +6560,33 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6589,10 +6594,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -6601,16 +6606,16 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6637,13 +6642,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -6661,19 +6666,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -6684,10 +6689,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6695,10 +6700,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -6707,16 +6712,16 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6743,13 +6748,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -6767,19 +6772,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -6790,10 +6795,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6801,10 +6806,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -6813,16 +6818,16 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6873,19 +6878,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -6896,10 +6901,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6907,10 +6912,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -6919,16 +6924,16 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6979,19 +6984,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -7002,10 +7007,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7013,10 +7018,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7025,16 +7030,16 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7085,19 +7090,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -7108,10 +7113,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7119,10 +7124,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7131,16 +7136,16 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7167,13 +7172,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7191,19 +7196,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -7214,10 +7219,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7225,10 +7230,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -7237,16 +7242,16 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7297,19 +7302,19 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -7320,10 +7325,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7331,10 +7336,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -7343,16 +7348,16 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7403,19 +7408,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -7426,10 +7431,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7437,10 +7442,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -7449,16 +7454,16 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7509,19 +7514,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -7532,10 +7537,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7543,10 +7548,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -7555,16 +7560,16 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7615,19 +7620,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -7638,10 +7643,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7649,10 +7654,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -7661,16 +7666,16 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7721,19 +7726,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -7744,10 +7749,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7755,10 +7760,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -7767,16 +7772,16 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7827,19 +7832,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -7850,10 +7855,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7861,10 +7866,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -7873,16 +7878,16 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7933,19 +7938,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -7956,10 +7961,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7967,10 +7972,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -7979,16 +7984,16 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8039,19 +8044,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -8062,10 +8067,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8073,10 +8078,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8085,16 +8090,16 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8145,19 +8150,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -8168,10 +8173,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8179,10 +8184,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -8194,13 +8199,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8251,13 +8256,13 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
@@ -8269,26 +8274,26 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -8300,16 +8305,16 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8359,68 +8364,68 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -8469,33 +8474,33 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8503,10 +8508,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -8515,16 +8520,16 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8575,19 +8580,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -8598,10 +8603,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8609,10 +8614,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -8621,16 +8626,16 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8681,19 +8686,19 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -8704,10 +8709,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8715,10 +8720,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -8727,16 +8732,16 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8787,19 +8792,19 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -8810,10 +8815,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8821,10 +8826,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -8833,16 +8838,16 @@
         <v>20</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8893,19 +8898,19 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -8916,10 +8921,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8927,10 +8932,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -8939,16 +8944,16 @@
         <v>20</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8999,19 +9004,19 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
@@ -9022,10 +9027,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9033,10 +9038,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -9045,16 +9050,16 @@
         <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9105,19 +9110,19 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -9128,10 +9133,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9139,10 +9144,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -9151,16 +9156,16 @@
         <v>20</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9211,19 +9216,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -9234,10 +9239,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9245,10 +9250,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -9257,16 +9262,16 @@
         <v>20</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9317,19 +9322,19 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -9340,10 +9345,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9351,10 +9356,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -9363,16 +9368,16 @@
         <v>20</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9423,19 +9428,19 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
@@ -9446,10 +9451,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9457,10 +9462,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -9472,13 +9477,13 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9529,13 +9534,13 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
@@ -9547,26 +9552,26 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -9578,16 +9583,16 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9637,68 +9642,68 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -9747,33 +9752,33 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9781,10 +9786,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -9793,16 +9798,16 @@
         <v>20</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9829,13 +9834,13 @@
         <v>20</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
@@ -9853,19 +9858,19 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -9876,10 +9881,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9887,10 +9892,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -9899,16 +9904,16 @@
         <v>20</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9959,19 +9964,19 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
@@ -9982,10 +9987,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9993,10 +9998,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -10005,16 +10010,16 @@
         <v>20</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10065,19 +10070,19 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -10088,10 +10093,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10099,10 +10104,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -10111,16 +10116,16 @@
         <v>20</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10171,19 +10176,19 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>20</v>
@@ -10194,10 +10199,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10205,10 +10210,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -10217,16 +10222,16 @@
         <v>20</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10277,19 +10282,19 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>20</v>
@@ -10300,10 +10305,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10311,10 +10316,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -10323,16 +10328,16 @@
         <v>20</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10383,19 +10388,19 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
@@ -10406,10 +10411,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10417,10 +10422,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -10429,16 +10434,16 @@
         <v>20</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10489,19 +10494,19 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>20</v>
@@ -10512,10 +10517,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10523,10 +10528,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -10535,16 +10540,16 @@
         <v>20</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10595,19 +10600,19 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
@@ -10618,10 +10623,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10629,10 +10634,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>20</v>
@@ -10644,13 +10649,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10701,13 +10706,13 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
@@ -10719,26 +10724,26 @@
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>20</v>
@@ -10750,16 +10755,16 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10809,68 +10814,68 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -10919,33 +10924,33 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10953,10 +10958,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>20</v>
@@ -10965,16 +10970,16 @@
         <v>20</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11001,13 +11006,13 @@
         <v>20</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -11025,19 +11030,19 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>20</v>
@@ -11048,10 +11053,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11059,10 +11064,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>20</v>
@@ -11071,16 +11076,16 @@
         <v>20</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11131,19 +11136,19 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>20</v>
@@ -11154,10 +11159,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11165,10 +11170,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>20</v>
@@ -11177,16 +11182,16 @@
         <v>20</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11237,19 +11242,19 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>20</v>
@@ -11260,10 +11265,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11271,10 +11276,10 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>20</v>
@@ -11283,16 +11288,16 @@
         <v>20</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11343,19 +11348,19 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>20</v>
@@ -11366,10 +11371,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11377,10 +11382,10 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>20</v>
@@ -11392,13 +11397,13 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11449,13 +11454,13 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>20</v>
@@ -11467,26 +11472,26 @@
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>20</v>
@@ -11498,16 +11503,16 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11557,68 +11562,68 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -11667,33 +11672,33 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11701,10 +11706,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>20</v>
@@ -11713,16 +11718,16 @@
         <v>20</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11773,19 +11778,19 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>20</v>
@@ -11796,10 +11801,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11807,10 +11812,10 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>20</v>
@@ -11819,16 +11824,16 @@
         <v>20</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11879,19 +11884,19 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>20</v>
@@ -11902,10 +11907,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11913,10 +11918,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>20</v>
@@ -11925,16 +11930,16 @@
         <v>20</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11985,19 +11990,19 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>20</v>
@@ -12008,10 +12013,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12019,10 +12024,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>20</v>
@@ -12034,13 +12039,13 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12091,13 +12096,13 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>20</v>
@@ -12109,26 +12114,26 @@
         <v>20</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>20</v>
@@ -12140,16 +12145,16 @@
         <v>20</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12199,68 +12204,68 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -12309,33 +12314,33 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12343,10 +12348,10 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>20</v>
@@ -12355,16 +12360,16 @@
         <v>20</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12415,19 +12420,19 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>20</v>
@@ -12438,10 +12443,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12449,10 +12454,10 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>20</v>
@@ -12461,16 +12466,16 @@
         <v>20</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -12521,19 +12526,19 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>20</v>
